--- a/sample_data/sample_assets.xlsx
+++ b/sample_data/sample_assets.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -997,12 +997,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ESX-001</t>
+          <t>VC-002</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>esxi-01</t>
+          <t>vcenter-02</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>192.0.2.31</t>
+          <t>192.0.2.32</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1022,15 +1022,19 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>ESXi</t>
+          <t>vCenter Server</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7.0 U3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:vmware:vcenter_server:6.7:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>중</t>
@@ -1048,19 +1052,19 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>CPE 없음 → Level 2 후보</t>
+          <t>Update 수준 미기재 → CVE-2021-21972 검토 필요(Level 3) 기대</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>WIN-001</t>
+          <t>ESX-001</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>win-ad-01</t>
+          <t>esxi-01</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1070,37 +1074,33 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>192.0.2.40</t>
+          <t>192.0.2.31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>VMware</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Windows Server 2022</t>
+          <t>ESXi</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10.0.20348.2582</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>cpe:2.3:o:microsoft:windows_server_2022:10.0.20348.2582:*:*:*:*:*:*:*</t>
-        </is>
-      </c>
+          <t>7.0 U3</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>가상담당자06</t>
+          <t>가상담당자05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1110,19 +1110,19 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Version Range: CVE-2024-38063(10.0.20348.2655 미만)</t>
+          <t>CPE 없음 → Level 2 후보</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>WIN-002</t>
+          <t>WIN-001</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>win-file-01</t>
+          <t>win-ad-01</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>192.0.2.41</t>
+          <t>192.0.2.40</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1147,17 +1147,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10.0.20348.2700</t>
+          <t>10.0.20348.2582</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>cpe:2.3:o:microsoft:windows_server_2022:10.0.20348.2700:*:*:*:*:*:*:*</t>
+          <t>cpe:2.3:o:microsoft:windows_server_2022:10.0.20348.2582:*:*:*:*:*:*:*</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1172,19 +1172,19 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Range 제외: CVE-2024-38063 미해당 기대</t>
+          <t>Version Range: CVE-2024-38063(10.0.20348.2655 미만)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LNX-001</t>
+          <t>WIN-002</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ubuntu-app-01</t>
+          <t>win-file-01</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1194,27 +1194,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>192.0.2.50</t>
+          <t>192.0.2.41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Canonical</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Ubuntu Linux</t>
+          <t>Windows Server 2022</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>10.0.20348.2700</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>cpe:2.3:o:canonical:ubuntu_linux:22.04:*:*:*:lts:*:*:*</t>
+          <t>cpe:2.3:o:microsoft:windows_server_2022:10.0.20348.2700:*:*:*:*:*:*:*</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1224,17 +1224,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>가상담당자07</t>
+          <t>가상담당자06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>가상개발팀</t>
+          <t>가상인프라팀</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>OS</t>
+          <t>Range 제외: CVE-2024-38063 미해당 기대</t>
         </is>
       </c>
     </row>
@@ -1261,22 +1261,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>OpenBSD</t>
+          <t>Canonical</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>OpenSSH</t>
+          <t>Ubuntu Linux</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>22.04</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>cpe:2.3:a:openbsd:openssh:8.9:p1:*:*:*:*:*:*</t>
+          <t>cpe:2.3:o:canonical:ubuntu_linux:22.04:*:*:*:lts:*:*:*</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1296,19 +1296,19 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>동일 자산 다중 제품: CVE-2024-6387(8.6~9.8), CVE-2023-38408</t>
+          <t>OS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>LNX-002</t>
+          <t>LNX-001</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>rhel-db-01</t>
+          <t>ubuntu-app-01</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1318,55 +1318,59 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>192.0.2.51</t>
+          <t>192.0.2.50</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>OpenBSD</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Linux</t>
+          <t>OpenSSH</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8.10</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:openbsd:openssh:8.9:p1:*:*:*:*:*:*</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>가상담당자08</t>
+          <t>가상담당자07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>가상DB팀</t>
+          <t>가상개발팀</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>CPE 없음 → Level 2 후보</t>
+          <t>동일 자산 다중 제품: CVE-2024-6387(8.6~9.8), CVE-2023-38408</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>DB-001</t>
+          <t>LNX-002</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>pg-db-01</t>
+          <t>rhel-db-01</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1376,29 +1380,25 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>192.0.2.60</t>
+          <t>192.0.2.51</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>PostgreSQL</t>
+          <t>Enterprise Linux</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13.11</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>cpe:2.3:a:postgresql:postgresql:13.11:*:*:*:*:*:*:*</t>
-        </is>
-      </c>
+          <t>8.10</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>상</t>
@@ -1416,19 +1416,19 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Version Range: CVE-2023-39417(13.0~13.12 미만)</t>
+          <t>CPE 없음 → Level 2 후보</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>DB-002</t>
+          <t>DB-001</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ora-db-01</t>
+          <t>pg-db-01</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1438,25 +1438,29 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>192.0.2.61</t>
+          <t>192.0.2.60</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>PostgreSQL</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Database Server</t>
+          <t>PostgreSQL</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19c</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
+          <t>13.11</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:postgresql:postgresql:13.11:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
           <t>상</t>
@@ -1474,19 +1478,19 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>CPE 없음 → Level 2 후보</t>
+          <t>Version Range: CVE-2023-39417(13.0~13.12 미만)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>APP-001</t>
+          <t>DB-002</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>app-batch-01</t>
+          <t>ora-db-01</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1496,7 +1500,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>192.0.2.70</t>
+          <t>192.0.2.61</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1506,45 +1510,45 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Java SE</t>
+          <t>Database Server</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8u401</t>
+          <t>19c</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>가상담당자09</t>
+          <t>가상담당자08</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>가상개발팀</t>
+          <t>가상DB팀</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>CPE 없음, 벤더 버전표기(8u401) → Level 2/검토</t>
+          <t>CPE 없음 → Level 2 후보</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>APP-002</t>
+          <t>APP-001</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>app-api-01</t>
+          <t>app-batch-01</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1554,7 +1558,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>192.0.2.71</t>
+          <t>192.0.2.70</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1564,19 +1568,15 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>JDK</t>
+          <t>Java SE</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17.0.2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>cpe:2.3:a:oracle:jdk:17.0.2:*:*:*:*:*:*:*</t>
-        </is>
-      </c>
+          <t>8u401</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
           <t>중</t>
@@ -1594,19 +1594,19 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>CPE Exact: CVE-2022-21449</t>
+          <t>CPE 없음, 벤더 버전표기(8u401) → Level 2/검토</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>APP-003</t>
+          <t>APP-002</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>app-log-01</t>
+          <t>app-api-01</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>192.0.2.72</t>
+          <t>192.0.2.71</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Apache</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Log4j</t>
+          <t>JDK</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2.14.1</t>
+          <t>17.0.2</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>cpe:2.3:a:apache:log4j:2.14.1:*:*:*:*:*:*:*</t>
+          <t>cpe:2.3:a:oracle:jdk:17.0.2:*:*:*:*:*:*:*</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1656,19 +1656,19 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Version Range: CVE-2021-44228(2.13.0~2.15.0 미만)</t>
+          <t>CPE Exact: CVE-2022-21449</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>APP-004</t>
+          <t>APP-003</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>build-01</t>
+          <t>app-log-01</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1678,37 +1678,37 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>192.0.2.73</t>
+          <t>192.0.2.72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Tukaani</t>
+          <t>Apache</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>XZ Utils</t>
+          <t>Log4j</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5.6.0</t>
+          <t>2.14.1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>cpe:2.3:a:tukaani:xz:5.6.0:*:*:*:*:*:*:*</t>
+          <t>cpe:2.3:a:apache:log4j:2.14.1:*:*:*:*:*:*:*</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>가상담당자10</t>
+          <t>가상담당자09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1718,19 +1718,19 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>CPE Exact: CVE-2024-3094</t>
+          <t>Version Range: CVE-2021-44228(2.13.0~2.15.0 미만)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>PC-001</t>
+          <t>APP-004</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>vdi-pc-01</t>
+          <t>build-01</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1740,27 +1740,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>192.0.2.80</t>
+          <t>192.0.2.73</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Tukaani</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Chrome</t>
+          <t>XZ Utils</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>116.0.5845.96</t>
+          <t>5.6.0</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>cpe:2.3:a:google:chrome:116.0.5845.96:*:*:*:*:*:*:*</t>
+          <t>cpe:2.3:a:tukaani:xz:5.6.0:*:*:*:*:*:*:*</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1770,29 +1770,29 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>가상담당자11</t>
+          <t>가상담당자10</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>가상사무팀</t>
+          <t>가상개발팀</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Version Range: CVE-2023-4863(116.0.5845.187 미만)</t>
+          <t>CPE Exact: CVE-2024-3094</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>PC-002</t>
+          <t>PC-001</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>vdi-pc-02</t>
+          <t>vdi-pc-01</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>192.0.2.81</t>
+          <t>192.0.2.80</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>129.0.6668.58</t>
+          <t>116.0.5845.96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>cpe:2.3:a:google:chrome:129.0.6668.58:*:*:*:*:*:*:*</t>
+          <t>cpe:2.3:a:google:chrome:116.0.5845.96:*:*:*:*:*:*:*</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1842,67 +1842,129 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Range 제외: CVE-2023-4863 미해당 기대</t>
+          <t>Version Range: CVE-2023-4863(116.0.5845.187 미만)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>PC-002</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>vdi-pc-02</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>내부</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>192.0.2.81</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Chrome</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>129.0.6668.58</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>cpe:2.3:a:google:chrome:129.0.6668.58:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>가상담당자11</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>가상사무팀</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Range 제외: CVE-2023-4863 미해당 기대</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>MAIL-001</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>mail-gw-01</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>경계면</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>203.0.113.25</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Mail Gateway</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>cpe:2.3:a:example:mail gateway:3.1</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>가상담당자12</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>가상보안팀</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>잘못된 CPE(공백·필드 부족) → 오류 표시 후 Level 2</t>
         </is>
@@ -1910,10 +1972,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="C2:C224" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C2:C225" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"경계면,내부"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I224" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="I2:I225" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"상,중,하"</formula1>
     </dataValidation>
   </dataValidations>
